--- a/data/trending_integrated_20261029_12.xlsx
+++ b/data/trending_integrated_20261029_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G2" t="n">
         <v>60</v>
-      </c>
-      <c r="F2" t="n">
-        <v>22</v>
-      </c>
-      <c r="G2" t="n">
-        <v>54</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>6722815509</v>
+        <v>6750475939</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9500</v>
+        <v>9390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.90%</t>
+          <t>'+17.52%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>122142555890</v>
+        <v>122870060815</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38150</v>
+        <v>38350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.63%</t>
+          <t>'+10.20%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.74</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>103503907350</v>
+        <v>104478796650</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7740</v>
+        <v>7670</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.89%</t>
+          <t>'+2.95%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G5" t="n">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>100866289825</v>
+        <v>102572951830</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>하이닉스 물량 완판 및 광주반도체 속도전 돌입 소식. 외국인, 기타법인 매수세 유입 확인. 광주 반도체 테마 상승 기대.</t>
+          <t>서산, 반도체 테마 기대감 속 외국인 및 기타법인 매수세 유입. '대장주'로서의 포지션 강조.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광주반도체', '테마', '외국인 매수']</t>
+          <t>['반도체테마', '외인매수', '대장주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29650</v>
+        <v>29400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.31%</t>
+          <t>'+2.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
         <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H6" t="n">
         <v>1.77</v>
@@ -978,7 +978,7 @@
         <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>97172375100</v>
+        <v>98155655850</v>
       </c>
       <c r="P6" t="n">
         <v>59600</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1518000</v>
+        <v>1516000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.08%</t>
+          <t>'+1.95%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G7" t="n">
-        <v>1142</v>
+        <v>1171</v>
       </c>
       <c r="H7" t="n">
         <v>48.66</v>
@@ -1070,7 +1070,7 @@
         <v>48.61</v>
       </c>
       <c r="O7" t="n">
-        <v>4581260095000</v>
+        <v>4632889000500</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자와 차별화된 움직임 기대. 최태원 회장의 경영 능력 긍정 평가. 국장 내 SK하이닉스의 대장주 역할 기대감.</t>
+          <t>SK하이닉스, 삼성전자와 차별화된 행보에 대한 기대감. 자사주 매입 효과 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['차별화', '대장주', '경영 능력']</t>
+          <t>['차별화', '자사주매입', '반등']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14480</v>
+        <v>14460</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.63%</t>
+          <t>'+0.49%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F8" t="n">
         <v>73</v>
       </c>
       <c r="G8" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H8" t="n">
         <v>8.050000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>50796443225</v>
+        <v>51220180590</v>
       </c>
       <c r="P8" t="n">
         <v>49800</v>
@@ -1222,13 +1222,13 @@
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F9" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G9" t="n">
-        <v>1423</v>
+        <v>1509</v>
       </c>
       <c r="H9" t="n">
         <v>24.78</v>
@@ -1254,7 +1254,7 @@
         <v>24.86</v>
       </c>
       <c r="O9" t="n">
-        <v>428235788000</v>
+        <v>433268452500</v>
       </c>
       <c r="P9" t="n">
         <v>723000</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>호실적 달성 및 컨센서스 상회. 전고체 배터리 상용화 기대감 및 미래 성장 전망.</t>
+          <t>삼성SDI, 호실적 발표 및 전고체 배터리 상용화 기대감. 성장 기업으로서 주주환원 불필요.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['호실적', '전고체 배터리', '컨센서스']</t>
+          <t>['호실적', '전고체배터리', '상용화']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15000</v>
+        <v>14940</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.13%</t>
+          <t>'-0.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F10" t="n">
         <v>79</v>
       </c>
       <c r="G10" t="n">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>137001359395</v>
+        <v>137962463405</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26550</v>
+        <v>26400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.56%</t>
+          <t>'-1.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="H11" t="n">
         <v>12.23</v>
@@ -1438,7 +1438,7 @@
         <v>12.3</v>
       </c>
       <c r="O11" t="n">
-        <v>33513370975</v>
+        <v>34379214125</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63200</v>
+        <v>62900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.56%</t>
+          <t>'-2.02%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G12" t="n">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="H12" t="n">
         <v>41.55</v>
@@ -1530,7 +1530,7 @@
         <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>141123057350</v>
+        <v>142751822050</v>
       </c>
       <c r="P12" t="n">
         <v>67300</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>184000</v>
+        <v>8860</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.21%</t>
+          <t>'-3.49%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>-0.37</v>
       </c>
       <c r="E13" t="n">
-        <v>133</v>
+        <v>65</v>
       </c>
       <c r="F13" t="n">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>398</v>
+        <v>166</v>
       </c>
       <c r="H13" t="n">
-        <v>75</v>
+        <v>0.37</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>190100</v>
+        <v>9180</v>
       </c>
       <c r="K13" t="n">
-        <v>189400</v>
+        <v>9200</v>
       </c>
       <c r="L13" t="n">
-        <v>197000</v>
+        <v>10900</v>
       </c>
       <c r="M13" t="n">
-        <v>181200</v>
+        <v>8730</v>
       </c>
       <c r="N13" t="n">
-        <v>74.90000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>1106114005250</v>
+        <v>29549116120</v>
       </c>
       <c r="P13" t="n">
-        <v>243500</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>71000</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-409000</v>
+        <v>-47000</v>
       </c>
       <c r="S13" t="n">
-        <v>-172000</v>
+        <v>-1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>오너 리스크와 초허접한 IR 언급. 주주환원 불확실성 및 증여세 관련 주가 누르기 의혹 제기. 우선주 매입 소각 기대.</t>
+          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['오너 리스크', '주주환원', '우선주']</t>
+          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8880</v>
+        <v>182700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.27%</t>
+          <t>'-3.89%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.37</v>
+        <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="G14" t="n">
-        <v>162</v>
+        <v>419</v>
       </c>
       <c r="H14" t="n">
-        <v>0.37</v>
+        <v>75</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,143 +1699,143 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>9180</v>
+        <v>190100</v>
       </c>
       <c r="K14" t="n">
-        <v>9200</v>
+        <v>189400</v>
       </c>
       <c r="L14" t="n">
-        <v>10900</v>
+        <v>197000</v>
       </c>
       <c r="M14" t="n">
-        <v>8730</v>
+        <v>181200</v>
       </c>
       <c r="N14" t="n">
-        <v>0.74</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>29490429540</v>
+        <v>1125184532450</v>
       </c>
       <c r="P14" t="n">
-        <v>19380</v>
+        <v>243500</v>
       </c>
       <c r="Q14" t="n">
-        <v>3200</v>
+        <v>71000</v>
       </c>
       <c r="R14" t="n">
-        <v>-47000</v>
+        <v>-409000</v>
       </c>
       <c r="S14" t="n">
-        <v>-1000</v>
+        <v>-172000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
+          <t>삼성전자우, 오너 리스크 및 허접한 IR에 대한 불만 표출. 주주환원 불확실성.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
+          <t>['오너리스크', 'IR', '주주환원']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4035</v>
+        <v>15810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.81%</t>
+          <t>'-4.24%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="F15" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="G15" t="n">
-        <v>286</v>
+        <v>357</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2</v>
+        <v>28.07</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4195</v>
+        <v>16510</v>
       </c>
       <c r="K15" t="n">
-        <v>4280</v>
+        <v>16380</v>
       </c>
       <c r="L15" t="n">
-        <v>4480</v>
+        <v>16440</v>
       </c>
       <c r="M15" t="n">
-        <v>3915</v>
+        <v>15770</v>
       </c>
       <c r="N15" t="n">
-        <v>1.2</v>
+        <v>28.03</v>
       </c>
       <c r="O15" t="n">
-        <v>160330979201</v>
+        <v>38689109650</v>
       </c>
       <c r="P15" t="n">
-        <v>8100</v>
+        <v>35350</v>
       </c>
       <c r="Q15" t="n">
-        <v>592</v>
+        <v>15770</v>
       </c>
       <c r="R15" t="n">
-        <v>-190000</v>
+        <v>-48000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-70000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>5G 상용화 성공 및 글로벌 기업 대규모 공급 시작 뉴스 기반 급등 기대. 광통신 섹터 주도주 가능성 및 미국 시장 인정 시 게임 오버 전망.</t>
+          <t>삼성중공업, 실적 발표 불확실성과 향후 전망에 대한 우려. 중국에 뒤쳐질 수 있다는 비관론.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['5G 상용화', '광통신', '대규모 공급']</t>
+          <t>['실적', '전망', '조선주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15850</v>
+        <v>3995</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.00%</t>
+          <t>'-4.77%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="F16" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="G16" t="n">
-        <v>336</v>
+        <v>291</v>
       </c>
       <c r="H16" t="n">
-        <v>28.07</v>
+        <v>2.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>16510</v>
+        <v>4195</v>
       </c>
       <c r="K16" t="n">
-        <v>16380</v>
+        <v>4280</v>
       </c>
       <c r="L16" t="n">
-        <v>16440</v>
+        <v>4480</v>
       </c>
       <c r="M16" t="n">
-        <v>15770</v>
+        <v>3915</v>
       </c>
       <c r="N16" t="n">
-        <v>28.03</v>
+        <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>37410155750</v>
+        <v>161223085509</v>
       </c>
       <c r="P16" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q16" t="n">
-        <v>15770</v>
+        <v>592</v>
       </c>
       <c r="R16" t="n">
-        <v>-48000</v>
+        <v>-190000</v>
       </c>
       <c r="S16" t="n">
-        <v>-70000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>신저점 갱신 및 실적 부진으로 인한 투자자 불만 고조. 중국 조선업체와의 경쟁 열세 및 한국 증권사의 부정적 영향력 언급.</t>
+          <t>5G 상용화 성공 및 글로벌 기업 대규모 공급 시작 뉴스 기반 급등 기대. 광통신 섹터 주도주 가능성 및 미국 시장 인정 시 게임 오버 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적 부진', '신저점', '조선업']</t>
+          <t>['5G 상용화', '광통신', '대규모 공급']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>229500</v>
+        <v>229250</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.17%</t>
+          <t>'-5.27%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="G17" t="n">
-        <v>2032</v>
+        <v>2121</v>
       </c>
       <c r="H17" t="n">
         <v>46.19</v>
@@ -1990,7 +1990,7 @@
         <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3827078766500</v>
+        <v>3863444666250</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주주환원 소극적인 경영 행태 및 이재용 불법 승계 의혹 제기. 컨퍼런스콜 수준 비판 및 족벌경영 세습경영 비판.</t>
+          <t>삼성전자, 주주환원 소극적 경영 및 이재용 불법 승계 세무조사 필요성 제기. 족벌경영 비판.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주주환원', '족벌경영', '컨퍼런스콜']</t>
+          <t>['주주환원', '족벌경영', '세무조사']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-10.90%</t>
+          <t>'-11.00%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H18" t="n">
         <v>5.35</v>
@@ -2082,7 +2082,7 @@
         <v>5.07</v>
       </c>
       <c r="O18" t="n">
-        <v>12023600458</v>
+        <v>12104546015</v>
       </c>
       <c r="P18" t="n">
         <v>4980</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>54300</v>
+        <v>54000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-11.56%</t>
+          <t>'-12.05%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="G19" t="n">
-        <v>2275</v>
+        <v>2234</v>
       </c>
       <c r="H19" t="n">
         <v>22.34</v>
@@ -2174,7 +2174,7 @@
         <v>22.32</v>
       </c>
       <c r="O19" t="n">
-        <v>264362864250</v>
+        <v>268117110150</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>체코 원전 시공사 협상 결렬에도 기자재 공급은 유지된다는 분석. 현 정부 및 특정 정치인 비판.</t>
+          <t>두산에너빌리티, 체코 원전 시공협상 결렬 관련 내용 왜곡 논란. 기자재 계약은 유지.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['체코 원전', '기자재', '시공사']</t>
+          <t>['체코원전', '시공협상', '기자재']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16730</v>
+        <v>16680</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-12.91%</t>
+          <t>'-13.17%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F20" t="n">
         <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>87221930775</v>
+        <v>87539055045</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회 가능성 및 반도체 대폭락 우려. 주가 하락 VI 발동 및 개미 털기 가능성 언급. 무지성 희망론 비판.</t>
+          <t>멜콘, 대규모 보호예수 물량 출회에 따른 급락 우려. 주포의 올릴 이유 없다는 분석.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체 대폭락', '개미 털기']</t>
+          <t>['보호예수', '급락', '주포']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2130</v>
+        <v>2100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-17.12%</t>
+          <t>'-18.29%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.47</v>
       </c>
       <c r="E21" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F21" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G21" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H21" t="n">
         <v>1.22</v>
@@ -2352,13 +2352,13 @@
         <v>2575</v>
       </c>
       <c r="M21" t="n">
-        <v>2115</v>
+        <v>2095</v>
       </c>
       <c r="N21" t="n">
         <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>14785673038</v>
+        <v>15241557032</v>
       </c>
       <c r="P21" t="n">
         <v>2965</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>전환사채 발행 및 매물 출회 가능성 제기. 주가 급락 및 투자자 답답함 호소.</t>
+          <t>삼기에너지솔루션즈, 주가 조작 의혹 및 반복적인 하락에 대한 불만 표출. 실적과 무관한 주가 움직임.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['전환사채', '매물폭탄', '실적']</t>
+          <t>['주가조작', '하락', '실적']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11390</v>
+        <v>11380</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-20.18%</t>
+          <t>'-20.25%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.23</v>
       </c>
       <c r="E22" t="n">
-        <v>771</v>
+        <v>787</v>
       </c>
       <c r="F22" t="n">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="G22" t="n">
-        <v>1876</v>
+        <v>1987</v>
       </c>
       <c r="H22" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>9.83</v>
       </c>
       <c r="O22" t="n">
-        <v>262875813690</v>
+        <v>265472332245</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>삼성증권 목표가 하향 및 대차 해지 도배, 공매도 세력 활동 의혹 제기. 원전 계약 관련 논란 속 공사비 협상 난항.</t>
+          <t>대우건설, 단기 과매도 상태에 삼성증권 목표가 하향 조정. 공매도 및 정치권 개입 의혹 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['공매도', '목표가 하향', '원전 계약']</t>
+          <t>['과매도', '공매도', '목표가']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261029_12.xlsx
+++ b/data/trending_integrated_20261029_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>6750475939</v>
+        <v>6777374979</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9390</v>
+        <v>9380</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.52%</t>
+          <t>'+17.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>122870060815</v>
+        <v>123572747285</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38350</v>
+        <v>38200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.20%</t>
+          <t>'+9.77%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>104478796650</v>
+        <v>105430989350</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7670</v>
+        <v>7770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.95%</t>
+          <t>'+4.30%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F5" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>102572951830</v>
+        <v>103505781600</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>서산, 반도체 테마 기대감 속 외국인 및 기타법인 매수세 유입. '대장주'로서의 포지션 강조.</t>
+          <t>반도체 테마 및 외인/기타법인 대량 매수세 유입을 근거로 주가 상승에 대한 기대감이 높으며, 광주 반도체 테마와의 연관성을 언급함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체테마', '외인매수', '대장주']</t>
+          <t>['반도체 테마', '외국인 매수', '광주 반도체']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29400</v>
+        <v>29150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.44%</t>
+          <t>'+1.57%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="H6" t="n">
         <v>1.77</v>
@@ -978,7 +978,7 @@
         <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>98155655850</v>
+        <v>99055590250</v>
       </c>
       <c r="P6" t="n">
         <v>59600</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1516000</v>
+        <v>1503000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.95%</t>
+          <t>'+1.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="G7" t="n">
-        <v>1171</v>
+        <v>1204</v>
       </c>
       <c r="H7" t="n">
         <v>48.66</v>
@@ -1070,7 +1070,7 @@
         <v>48.61</v>
       </c>
       <c r="O7" t="n">
-        <v>4632889000500</v>
+        <v>4709065137000</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>SK하이닉스, 삼성전자와 차별화된 행보에 대한 기대감. 자사주 매입 효과 언급.</t>
+          <t>삼성전자와는 다른 움직임을 보이며 독자적인 상승 추세를 기대하는 의견이 있으며, 최태원 회장의 경영 능력에 대한 긍정적 평가와 함께 자사주 매입 효과를 언급함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['차별화', '자사주매입', '반등']</t>
+          <t>['SK하이닉스', '삼성전자', '자사주 매입']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14460</v>
+        <v>14525</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.49%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F8" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="H8" t="n">
         <v>8.050000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>51220180590</v>
+        <v>51742623485</v>
       </c>
       <c r="P8" t="n">
         <v>49800</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>536000</v>
+        <v>535000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.37%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F9" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G9" t="n">
-        <v>1509</v>
+        <v>1590</v>
       </c>
       <c r="H9" t="n">
         <v>24.78</v>
@@ -1254,7 +1254,7 @@
         <v>24.86</v>
       </c>
       <c r="O9" t="n">
-        <v>433268452500</v>
+        <v>439496744000</v>
       </c>
       <c r="P9" t="n">
         <v>723000</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14940</v>
+        <v>14890</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.27%</t>
+          <t>'-0.60%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F10" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G10" t="n">
-        <v>702</v>
+        <v>722</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>137962463405</v>
+        <v>138885280830</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>메타 관련 뉴스 및 3분기 전망 긍정적. 루멘텀 인수설 및 미국장 광통신 섹터 급등 영향 기대. 연말 3만 목표.</t>
+          <t>광통신 섹터 강세와 루멘텀 인수 가능성 등 긍정적인 뉴스를 바탕으로 연말 목표 주가 3만원을 제시하며 상승 추세를 전망함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['메타', '광통신', '루멘텀 인수설']</t>
+          <t>['광통신', '루멘텀 인수', '유리기판']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26400</v>
+        <v>26350</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.12%</t>
+          <t>'-1.31%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H11" t="n">
         <v>12.23</v>
@@ -1438,7 +1438,7 @@
         <v>12.3</v>
       </c>
       <c r="O11" t="n">
-        <v>34379214125</v>
+        <v>35128707150</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1498,13 +1498,13 @@
         <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F12" t="n">
         <v>64</v>
       </c>
       <c r="G12" t="n">
-        <v>548</v>
+        <v>571</v>
       </c>
       <c r="H12" t="n">
         <v>41.55</v>
@@ -1530,7 +1530,7 @@
         <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>142751822050</v>
+        <v>144969369250</v>
       </c>
       <c r="P12" t="n">
         <v>67300</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 관련 긍정적 신호 포착. 수소 에너지 사업 기대감과 함께 신고가 경신 가능성에 대한 전망 제시.</t>
+          <t>자사주 매입 및 소각, 수주 공시 등을 기반으로 신고가 돌파 및 상승 추세를 기대하는 긍정적인 전망이 다수이며, 기관의 차익 실현 가능성도 언급됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8860</v>
+        <v>8850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.49%</t>
+          <t>'-3.59%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H13" t="n">
         <v>0.37</v>
@@ -1622,7 +1622,7 @@
         <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>29549116120</v>
+        <v>29671734280</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>182700</v>
+        <v>15790</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.89%</t>
+          <t>'-4.36%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F14" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="G14" t="n">
-        <v>419</v>
+        <v>366</v>
       </c>
       <c r="H14" t="n">
-        <v>75</v>
+        <v>28.07</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>190100</v>
+        <v>16510</v>
       </c>
       <c r="K14" t="n">
-        <v>189400</v>
+        <v>16380</v>
       </c>
       <c r="L14" t="n">
-        <v>197000</v>
+        <v>16440</v>
       </c>
       <c r="M14" t="n">
-        <v>181200</v>
+        <v>15770</v>
       </c>
       <c r="N14" t="n">
-        <v>74.90000000000001</v>
+        <v>28.03</v>
       </c>
       <c r="O14" t="n">
-        <v>1125184532450</v>
+        <v>41089893605</v>
       </c>
       <c r="P14" t="n">
-        <v>243500</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>71000</v>
+        <v>15770</v>
       </c>
       <c r="R14" t="n">
-        <v>-409000</v>
+        <v>-48000</v>
       </c>
       <c r="S14" t="n">
-        <v>-172000</v>
+        <v>-70000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼성전자우, 오너 리스크 및 허접한 IR에 대한 불만 표출. 주주환원 불확실성.</t>
+          <t>삼성중공업, 실적 발표 불확실성과 향후 전망에 대한 우려. 중국에 뒤쳐질 수 있다는 비관론.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['오너리스크', 'IR', '주주환원']</t>
+          <t>['실적', '전망', '조선주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15810</v>
+        <v>4010</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.24%</t>
+          <t>'-4.41%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="F15" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G15" t="n">
-        <v>357</v>
+        <v>308</v>
       </c>
       <c r="H15" t="n">
-        <v>28.07</v>
+        <v>2.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>16510</v>
+        <v>4195</v>
       </c>
       <c r="K15" t="n">
-        <v>16380</v>
+        <v>4280</v>
       </c>
       <c r="L15" t="n">
-        <v>16440</v>
+        <v>4480</v>
       </c>
       <c r="M15" t="n">
-        <v>15770</v>
+        <v>3915</v>
       </c>
       <c r="N15" t="n">
-        <v>28.03</v>
+        <v>1.2</v>
       </c>
       <c r="O15" t="n">
-        <v>38689109650</v>
+        <v>161877321696</v>
       </c>
       <c r="P15" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q15" t="n">
-        <v>15770</v>
+        <v>592</v>
       </c>
       <c r="R15" t="n">
-        <v>-48000</v>
+        <v>-190000</v>
       </c>
       <c r="S15" t="n">
-        <v>-70000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성중공업, 실적 발표 불확실성과 향후 전망에 대한 우려. 중국에 뒤쳐질 수 있다는 비관론.</t>
+          <t>광통신 섹터 강세 및 5G 상용화 관련 뉴스에도 불구하고 주가 하락에 대한 불만과 개잡주라는 비판이 존재하며, 단기 트레이딩 관점이 엿보임.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['실적', '전망', '조선주']</t>
+          <t>['광통신', '5G 상용화', '개잡주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,86 +1844,86 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3995</v>
+        <v>181400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.77%</t>
+          <t>'-4.58%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="F16" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="G16" t="n">
-        <v>291</v>
+        <v>438</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2</v>
+        <v>75</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4195</v>
+        <v>190100</v>
       </c>
       <c r="K16" t="n">
-        <v>4280</v>
+        <v>189400</v>
       </c>
       <c r="L16" t="n">
-        <v>4480</v>
+        <v>197000</v>
       </c>
       <c r="M16" t="n">
-        <v>3915</v>
+        <v>181100</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>161223085509</v>
+        <v>1157151284200</v>
       </c>
       <c r="P16" t="n">
-        <v>8100</v>
+        <v>243500</v>
       </c>
       <c r="Q16" t="n">
-        <v>592</v>
+        <v>71000</v>
       </c>
       <c r="R16" t="n">
-        <v>-190000</v>
+        <v>-409000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-172000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>5G 상용화 성공 및 글로벌 기업 대규모 공급 시작 뉴스 기반 급등 기대. 광통신 섹터 주도주 가능성 및 미국 시장 인정 시 게임 오버 전망.</t>
+          <t>오너 리스크, 주주환원 불확실성, 허술한 IR 등 삼성전자우에 대한 부정적 평가가 많으며, 증여세 문제와 연관된 주가 부양 의혹이 제기됨.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['5G 상용화', '광통신', '대규모 공급']</t>
+          <t>['오너 리스크', '주주환원', 'IR']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>229250</v>
+        <v>227250</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.27%</t>
+          <t>'-6.10%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="G17" t="n">
-        <v>2121</v>
+        <v>2246</v>
       </c>
       <c r="H17" t="n">
         <v>46.19</v>
@@ -1990,7 +1990,7 @@
         <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3863444666250</v>
+        <v>3939111900250</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>삼성전자, 주주환원 소극적 경영 및 이재용 불법 승계 세무조사 필요성 제기. 족벌경영 비판.</t>
+          <t>주주환원 소극성, 이재용 경영 능력 비판 등 부정적 의견이 지배적이며, 세계 1위 기업으로서의 행동이 미흡하다는 지적이 있음.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주주환원', '족벌경영', '세무조사']</t>
+          <t>['주주환원', '이재용', '컨퍼런스콜']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1869</v>
+        <v>1851</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-11.00%</t>
+          <t>'-11.86%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H18" t="n">
         <v>5.35</v>
@@ -2082,7 +2082,7 @@
         <v>5.07</v>
       </c>
       <c r="O18" t="n">
-        <v>12104546015</v>
+        <v>12309302297</v>
       </c>
       <c r="P18" t="n">
         <v>4980</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>54000</v>
+        <v>53900</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-12.05%</t>
+          <t>'-12.21%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G19" t="n">
-        <v>2234</v>
+        <v>2135</v>
       </c>
       <c r="H19" t="n">
         <v>22.34</v>
@@ -2174,7 +2174,7 @@
         <v>22.32</v>
       </c>
       <c r="O19" t="n">
-        <v>268117110150</v>
+        <v>277056015550</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 체코 원전 시공협상 결렬 관련 내용 왜곡 논란. 기자재 계약은 유지.</t>
+          <t>체코 원전 시공사 변경 관련 내용이 두산에너빌리티와 무관하다는 의견이 있으나, 정치적 이슈로 인해 주가가 하락하고 있으며 명확한 공시 부재에 대한 비판이 있음.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['체코원전', '시공협상', '기자재']</t>
+          <t>['체코 원전', '시공사 변경', '기자재 계약']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16680</v>
+        <v>16440</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-13.17%</t>
+          <t>'-14.42%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2260,13 +2260,13 @@
         <v>19840</v>
       </c>
       <c r="M20" t="n">
-        <v>16400</v>
+        <v>16360</v>
       </c>
       <c r="N20" t="n">
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>87539055045</v>
+        <v>88349880935</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-18.29%</t>
+          <t>'-18.68%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.47</v>
       </c>
       <c r="E21" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G21" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="H21" t="n">
         <v>1.22</v>
@@ -2352,13 +2352,13 @@
         <v>2575</v>
       </c>
       <c r="M21" t="n">
-        <v>2095</v>
+        <v>2085</v>
       </c>
       <c r="N21" t="n">
         <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>15241557032</v>
+        <v>15533950745</v>
       </c>
       <c r="P21" t="n">
         <v>2965</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈, 주가 조작 의혹 및 반복적인 하락에 대한 불만 표출. 실적과 무관한 주가 움직임.</t>
+          <t>실적 부진 및 주가 조작 의혹 등 부정적인 내용만 있으며, 주가 하락에 대한 불만과 함께 종목에 대한 신뢰도가 낮음을 시사함.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가조작', '하락', '실적']</t>
+          <t>['실적 부진', '주가 조작', '사채 발행']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11380</v>
+        <v>11550</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-20.25%</t>
+          <t>'-19.06%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.23</v>
       </c>
       <c r="E22" t="n">
-        <v>787</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G22" t="n">
-        <v>1987</v>
+        <v>2038</v>
       </c>
       <c r="H22" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>9.83</v>
       </c>
       <c r="O22" t="n">
-        <v>265472332245</v>
+        <v>271711586100</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>대우건설, 단기 과매도 상태에 삼성증권 목표가 하향 조정. 공매도 및 정치권 개입 의혹 제기.</t>
+          <t>원전 공사 관련 악재와 삼성증권 목표가 하향에도 불구하고, 일부에서는 정치권 개입 및 과매도 가능성을 제기하며 반등을 기대하고 있음.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['과매도', '공매도', '목표가']</t>
+          <t>['원전 공사', '목표가 하향', '과매도']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261029_12.xlsx
+++ b/data/trending_integrated_20261029_12.xlsx
@@ -578,10 +578,10 @@
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
         <v>68</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>6777374979</v>
+        <v>6803732359</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9380</v>
+        <v>9340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.40%</t>
+          <t>'+16.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3" t="n">
         <v>75</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>123572747285</v>
+        <v>124376564530</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -762,13 +762,13 @@
         <v>-0.74</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>105430989350</v>
+        <v>106346824425</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7770</v>
+        <v>7730</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.30%</t>
+          <t>'+3.76%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G5" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>103505781600</v>
+        <v>104386742945</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>반도체 테마 및 외인/기타법인 대량 매수세 유입을 근거로 주가 상승에 대한 기대감이 높으며, 광주 반도체 테마와의 연관성을 언급함.</t>
+          <t>반도체 테마 및 광주 반도체 클러스터 관련 긍정적 전망. 외국인 및 기타법인 매수세 유입 확인. 차트상 상승 추세 및 텐베거 가능성 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체 테마', '외국인 매수', '광주 반도체']</t>
+          <t>['반도체 테마', '외국인 매수', '차트 분석']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29150</v>
+        <v>29050</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.57%</t>
+          <t>'+1.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H6" t="n">
         <v>1.77</v>
@@ -978,7 +978,7 @@
         <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>99055590250</v>
+        <v>99925924050</v>
       </c>
       <c r="P6" t="n">
         <v>59600</v>
@@ -1044,7 +1044,7 @@
         <v>481</v>
       </c>
       <c r="G7" t="n">
-        <v>1204</v>
+        <v>1166</v>
       </c>
       <c r="H7" t="n">
         <v>48.66</v>
@@ -1070,7 +1070,7 @@
         <v>48.61</v>
       </c>
       <c r="O7" t="n">
-        <v>4709065137000</v>
+        <v>4782652149000</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자와는 다른 움직임을 보이며 독자적인 상승 추세를 기대하는 의견이 있으며, 최태원 회장의 경영 능력에 대한 긍정적 평가와 함께 자사주 매입 효과를 언급함.</t>
+          <t>삼성전자와의 비교를 통한 SK하이닉스의 상대적 우위 부각. 외인 매수세 유입 및 자사주 매입 효과에 대한 기대감. 향후 시가총액 1위 탈환 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '삼성전자', '자사주 매입']</t>
+          <t>['SK하이닉스', '삼성전자', '외인 매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14525</v>
+        <v>535000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>119</v>
+        <v>327</v>
       </c>
       <c r="F8" t="n">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="G8" t="n">
-        <v>312</v>
+        <v>1642</v>
       </c>
       <c r="H8" t="n">
-        <v>8.050000000000001</v>
+        <v>24.78</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14390</v>
+        <v>534000</v>
       </c>
       <c r="K8" t="n">
-        <v>15450</v>
+        <v>546000</v>
       </c>
       <c r="L8" t="n">
-        <v>16290</v>
+        <v>563000</v>
       </c>
       <c r="M8" t="n">
-        <v>14040</v>
+        <v>512000</v>
       </c>
       <c r="N8" t="n">
-        <v>8.109999999999999</v>
+        <v>24.86</v>
       </c>
       <c r="O8" t="n">
-        <v>51742623485</v>
+        <v>443997596500</v>
       </c>
       <c r="P8" t="n">
-        <v>49800</v>
+        <v>723000</v>
       </c>
       <c r="Q8" t="n">
-        <v>8180</v>
+        <v>259000</v>
       </c>
       <c r="R8" t="n">
-        <v>-238000</v>
+        <v>-24000</v>
       </c>
       <c r="S8" t="n">
-        <v>11000</v>
+        <v>9000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>의료 AI 섹터 강세 속 미국 나스닥 급등. 단주 매매 및 털고 나가는 움직임 포착. 공매도 세력에 대한 비판.</t>
+          <t>컨퍼런스콜 기반의 4분기 실적 컨센서스 상회 및 전고체 배터리 상용화 기대. 긍정적인 실적 발표와 미래 전망을 근거로 한 상승 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['의료 AI', '나스닥', '공매도']</t>
+          <t>['전고체배터리', '컨퍼런스콜', '실적']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>535000</v>
+        <v>14400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.19%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>324</v>
+        <v>119</v>
       </c>
       <c r="F9" t="n">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>1590</v>
+        <v>323</v>
       </c>
       <c r="H9" t="n">
-        <v>24.78</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>534000</v>
+        <v>14390</v>
       </c>
       <c r="K9" t="n">
-        <v>546000</v>
+        <v>15450</v>
       </c>
       <c r="L9" t="n">
-        <v>563000</v>
+        <v>16290</v>
       </c>
       <c r="M9" t="n">
-        <v>512000</v>
+        <v>14040</v>
       </c>
       <c r="N9" t="n">
-        <v>24.86</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>439496744000</v>
+        <v>52324939160</v>
       </c>
       <c r="P9" t="n">
-        <v>723000</v>
+        <v>49800</v>
       </c>
       <c r="Q9" t="n">
-        <v>259000</v>
+        <v>8180</v>
       </c>
       <c r="R9" t="n">
-        <v>-24000</v>
+        <v>-238000</v>
       </c>
       <c r="S9" t="n">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성SDI, 호실적 발표 및 전고체 배터리 상용화 기대감. 성장 기업으로서 주주환원 불필요.</t>
+          <t>미국 의료 AI 급등과 함께 일부 긍정적 언급이 있으나, 시장 약세 및 차익실현 가능성에 대한 우려 혼재. 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['호실적', '전고체배터리', '상용화']</t>
+          <t>['의료AI', '공매도', '차익실현']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14890</v>
+        <v>14880</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.60%</t>
+          <t>'-0.67%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F10" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G10" t="n">
-        <v>722</v>
+        <v>739</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>138885280830</v>
+        <v>139983357115</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1412,7 +1412,7 @@
         <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="H11" t="n">
         <v>12.23</v>
@@ -1438,7 +1438,7 @@
         <v>12.3</v>
       </c>
       <c r="O11" t="n">
-        <v>35128707150</v>
+        <v>35544772025</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1498,13 +1498,13 @@
         <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="F12" t="n">
         <v>64</v>
       </c>
       <c r="G12" t="n">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="H12" t="n">
         <v>41.55</v>
@@ -1530,7 +1530,7 @@
         <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>144969369250</v>
+        <v>147432446000</v>
       </c>
       <c r="P12" t="n">
         <v>67300</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각, 수주 공시 등을 기반으로 신고가 돌파 및 상승 추세를 기대하는 긍정적인 전망이 다수이며, 기관의 차익 실현 가능성도 언급됨.</t>
+          <t>자사주 매입 및 소각 기대감과 공매도 세력에 대한 경계. 수주 공시 및 신고가 돌파 가능성 언급. 삼성전자 시설 투자 확대 수혜 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['자사주 소각', '수주 공시', '신고가']</t>
+          <t>['자사주 매입', '수주 공시', '삼성전자 투자']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8850</v>
+        <v>8830</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.59%</t>
+          <t>'-3.81%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.37</v>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F13" t="n">
         <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H13" t="n">
         <v>0.37</v>
@@ -1622,7 +1622,7 @@
         <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>29671734280</v>
+        <v>29819929380</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15790</v>
+        <v>15760</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.36%</t>
+          <t>'-4.54%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F14" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G14" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H14" t="n">
         <v>28.07</v>
@@ -1708,19 +1708,19 @@
         <v>16440</v>
       </c>
       <c r="M14" t="n">
-        <v>15770</v>
+        <v>15760</v>
       </c>
       <c r="N14" t="n">
         <v>28.03</v>
       </c>
       <c r="O14" t="n">
-        <v>41089893605</v>
+        <v>42231718615</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>15770</v>
+        <v>15760</v>
       </c>
       <c r="R14" t="n">
         <v>-48000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼성중공업, 실적 발표 불확실성과 향후 전망에 대한 우려. 중국에 뒤쳐질 수 있다는 비관론.</t>
+          <t>실적 발표 후 주가 하락에 대한 실망감. 중국 조선업체와의 경쟁력 약화 및 향후 전망에 대한 우려. 한국 증권사의 신뢰성 문제 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적', '전망', '조선주']</t>
+          <t>['실적 발표', '조선업', '주가 하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,79 +1759,79 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4010</v>
+        <v>181000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.41%</t>
+          <t>'-4.79%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="F15" t="n">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="G15" t="n">
-        <v>308</v>
+        <v>444</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2</v>
+        <v>75</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4195</v>
+        <v>190100</v>
       </c>
       <c r="K15" t="n">
-        <v>4280</v>
+        <v>189400</v>
       </c>
       <c r="L15" t="n">
-        <v>4480</v>
+        <v>197000</v>
       </c>
       <c r="M15" t="n">
-        <v>3915</v>
+        <v>180800</v>
       </c>
       <c r="N15" t="n">
-        <v>1.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>161877321696</v>
+        <v>1175900121400</v>
       </c>
       <c r="P15" t="n">
-        <v>8100</v>
+        <v>243500</v>
       </c>
       <c r="Q15" t="n">
-        <v>592</v>
+        <v>71000</v>
       </c>
       <c r="R15" t="n">
-        <v>-190000</v>
+        <v>-409000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-172000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>광통신 섹터 강세 및 5G 상용화 관련 뉴스에도 불구하고 주가 하락에 대한 불만과 개잡주라는 비판이 존재하며, 단기 트레이딩 관점이 엿보임.</t>
+          <t>오너 리스크와 주주환원 불확실성에 대한 우려. IR 자료 및 컨퍼런스콜 내용의 허술함 지적. 증여세 문제와 연관된 주가 하락 및 우선주 소각 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '5G 상용화', '개잡주']</t>
+          <t>['오너 리스크', '주주환원', '우선주']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>181400</v>
+        <v>3980</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.58%</t>
+          <t>'-5.13%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="F16" t="n">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="G16" t="n">
-        <v>438</v>
+        <v>315</v>
       </c>
       <c r="H16" t="n">
-        <v>75</v>
+        <v>2.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>190100</v>
+        <v>4195</v>
       </c>
       <c r="K16" t="n">
-        <v>189400</v>
+        <v>4280</v>
       </c>
       <c r="L16" t="n">
-        <v>197000</v>
+        <v>4480</v>
       </c>
       <c r="M16" t="n">
-        <v>181100</v>
+        <v>3915</v>
       </c>
       <c r="N16" t="n">
-        <v>74.90000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1157151284200</v>
+        <v>162427647320</v>
       </c>
       <c r="P16" t="n">
-        <v>243500</v>
+        <v>8100</v>
       </c>
       <c r="Q16" t="n">
-        <v>71000</v>
+        <v>592</v>
       </c>
       <c r="R16" t="n">
-        <v>-409000</v>
+        <v>-190000</v>
       </c>
       <c r="S16" t="n">
-        <v>-172000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>오너 리스크, 주주환원 불확실성, 허술한 IR 등 삼성전자우에 대한 부정적 평가가 많으며, 증여세 문제와 연관된 주가 부양 의혹이 제기됨.</t>
+          <t>글로벌 기업 공급 시작 및 5G 상용화 관련 긍정적 뉴스에도 불구하고 주가 하락. 미국 시장 진출의 어려움 및 광통신 섹터 내 경쟁 심화 우려. 단타 세력의 차익 실현.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['오너 리스크', '주주환원', 'IR']</t>
+          <t>['5G 상용화', '광통신', '미국 시장']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>227250</v>
+        <v>227500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.10%</t>
+          <t>'-5.99%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="G17" t="n">
-        <v>2246</v>
+        <v>2415</v>
       </c>
       <c r="H17" t="n">
         <v>46.19</v>
@@ -1990,7 +1990,7 @@
         <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3939111900250</v>
+        <v>4020331899500</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주주환원 소극성, 이재용 경영 능력 비판 등 부정적 의견이 지배적이며, 세계 1위 기업으로서의 행동이 미흡하다는 지적이 있음.</t>
+          <t>컨퍼런스콜 내용에 대한 강한 불만과 경영진 퇴출 요구. 이재용 회장의 경영 능력 및 주주 무시에 대한 비판. 증여세 회피를 위한 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주주환원', '이재용', '컨퍼런스콜']</t>
+          <t>['컨퍼런스콜', '이재용', '증여세']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-11.86%</t>
+          <t>'-11.95%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H18" t="n">
         <v>5.35</v>
@@ -2082,7 +2082,7 @@
         <v>5.07</v>
       </c>
       <c r="O18" t="n">
-        <v>12309302297</v>
+        <v>12508469514</v>
       </c>
       <c r="P18" t="n">
         <v>4980</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53900</v>
+        <v>53800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-12.21%</t>
+          <t>'-12.38%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="G19" t="n">
-        <v>2135</v>
+        <v>2144</v>
       </c>
       <c r="H19" t="n">
         <v>22.34</v>
@@ -2174,7 +2174,7 @@
         <v>22.32</v>
       </c>
       <c r="O19" t="n">
-        <v>277056015550</v>
+        <v>281306395850</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>체코 원전 시공사 변경 관련 내용이 두산에너빌리티와 무관하다는 의견이 있으나, 정치적 이슈로 인해 주가가 하락하고 있으며 명확한 공시 부재에 대한 비판이 있음.</t>
+          <t>체코 원전 사업 시공사 변경 이슈에 대한 혼란 및 분석. 두산에너빌리티 자체는 기자재 공급사로 직접적인 영향이 적다는 의견. 정부 정책 및 정치권 개입에 대한 비판.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['체코 원전', '시공사 변경', '기자재 계약']</t>
+          <t>['체코 원전', '시공사 변경', '기자재 공급']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16440</v>
+        <v>16610</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-14.42%</t>
+          <t>'-13.53%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F20" t="n">
         <v>57</v>
       </c>
       <c r="G20" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2260,13 +2260,13 @@
         <v>19840</v>
       </c>
       <c r="M20" t="n">
-        <v>16360</v>
+        <v>16280</v>
       </c>
       <c r="N20" t="n">
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>88349880935</v>
+        <v>89139011875</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>멜콘, 대규모 보호예수 물량 출회에 따른 급락 우려. 주포의 올릴 이유 없다는 분석.</t>
+          <t>보호예수 물량 폭탄 우려 속 하락 전망. 반도체 호황에도 불구하고 개별적인 악재에 대한 부정적 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '급락', '주포']</t>
+          <t>['보호예수', '반도체', '하락']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2090</v>
+        <v>2100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-18.68%</t>
+          <t>'-18.29%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.47</v>
       </c>
       <c r="E21" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F21" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G21" t="n">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="H21" t="n">
         <v>1.22</v>
@@ -2358,7 +2358,7 @@
         <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>15533950745</v>
+        <v>15709176545</v>
       </c>
       <c r="P21" t="n">
         <v>2965</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>실적 부진 및 주가 조작 의혹 등 부정적인 내용만 있으며, 주가 하락에 대한 불만과 함께 종목에 대한 신뢰도가 낮음을 시사함.</t>
+          <t>실적 부진 및 급격한 주가 하락에 대한 불만. 기타법인 꾸준한 매집에도 불구하고 반등 없는 흐름 지적. 사채 발행 및 롤링 이슈에 대한 우려.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['실적 부진', '주가 조작', '사채 발행']</t>
+          <t>['주가 하락', '기타법인', '사채 발행']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11550</v>
+        <v>11540</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-19.06%</t>
+          <t>'-19.13%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G22" t="n">
-        <v>2038</v>
+        <v>2043</v>
       </c>
       <c r="H22" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>9.83</v>
       </c>
       <c r="O22" t="n">
-        <v>271711586100</v>
+        <v>276525474500</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>원전 공사 관련 악재와 삼성증권 목표가 하향에도 불구하고, 일부에서는 정치권 개입 및 과매도 가능성을 제기하며 반등을 기대하고 있음.</t>
+          <t>원전 공사 관련 단기 악재 및 과매도 진단. 정치권 개입 및 정부 태도에 대한 비판. 공사비 감액 및 재협상 과정에서 발생한 이슈에 대한 불만.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['원전 공사', '목표가 하향', '과매도']</t>
+          <t>['원전 공사', '과매도', '정치권 개입']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261029_12.xlsx
+++ b/data/trending_integrated_20261029_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
         <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>6803732359</v>
+        <v>6804233139</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9340</v>
+        <v>9300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.90%</t>
+          <t>'+16.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>124376564530</v>
+        <v>124834462590</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38200</v>
+        <v>38300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.77%</t>
+          <t>'+10.06%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>106346824425</v>
+        <v>107174468325</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7730</v>
+        <v>7770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.76%</t>
+          <t>'+4.30%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F5" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G5" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>104386742945</v>
+        <v>104637289155</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -931,267 +931,267 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29050</v>
+        <v>1512000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.22%</t>
+          <t>'+1.68%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>488</v>
       </c>
       <c r="G6" t="n">
-        <v>69</v>
+        <v>1176</v>
       </c>
       <c r="H6" t="n">
-        <v>1.77</v>
+        <v>48.66</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>28700</v>
+        <v>1487000</v>
       </c>
       <c r="K6" t="n">
-        <v>29150</v>
+        <v>1511000</v>
       </c>
       <c r="L6" t="n">
-        <v>31400</v>
+        <v>1587000</v>
       </c>
       <c r="M6" t="n">
-        <v>28350</v>
+        <v>1479000</v>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>48.61</v>
       </c>
       <c r="O6" t="n">
-        <v>99925924050</v>
+        <v>4841291423000</v>
       </c>
       <c r="P6" t="n">
-        <v>59600</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>1850</v>
+        <v>501000</v>
       </c>
       <c r="R6" t="n">
-        <v>44000</v>
+        <v>337000</v>
       </c>
       <c r="S6" t="n">
-        <v>11000</v>
+        <v>-93000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>루멘텀홀딩스 인수 관련 호재 및 기관 매수세 언급. 광통신주 동반 하락으로 인한 관망세.</t>
+          <t>삼성전자와의 비교를 통한 SK하이닉스의 상대적 우위 부각. 외인 매수세 유입 및 자사주 매입 효과에 대한 기대감. 향후 시가총액 1위 탈환 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['루멘텀', '기관']</t>
+          <t>['SK하이닉스', '삼성전자', '외인 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1503000</v>
+        <v>29150</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.08%</t>
+          <t>'+1.57%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>38</v>
       </c>
       <c r="F7" t="n">
-        <v>481</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>1166</v>
+        <v>66</v>
       </c>
       <c r="H7" t="n">
-        <v>48.66</v>
+        <v>1.77</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1487000</v>
+        <v>28700</v>
       </c>
       <c r="K7" t="n">
-        <v>1511000</v>
+        <v>29150</v>
       </c>
       <c r="L7" t="n">
-        <v>1587000</v>
+        <v>31400</v>
       </c>
       <c r="M7" t="n">
-        <v>1479000</v>
+        <v>28350</v>
       </c>
       <c r="N7" t="n">
-        <v>48.61</v>
+        <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>4782652149000</v>
+        <v>100590088050</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>59600</v>
       </c>
       <c r="Q7" t="n">
-        <v>501000</v>
+        <v>1850</v>
       </c>
       <c r="R7" t="n">
-        <v>337000</v>
+        <v>44000</v>
       </c>
       <c r="S7" t="n">
-        <v>-93000</v>
+        <v>11000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자와의 비교를 통한 SK하이닉스의 상대적 우위 부각. 외인 매수세 유입 및 자사주 매입 효과에 대한 기대감. 향후 시가총액 1위 탈환 가능성 언급.</t>
+          <t>루멘텀홀딩스 인수 관련 호재 및 기관 매수세 언급. 광통신주 동반 하락으로 인한 관망세.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '삼성전자', '외인 매수']</t>
+          <t>['루멘텀', '기관']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>535000</v>
+        <v>14510</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.19%</t>
+          <t>'+0.83%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>327</v>
+        <v>120</v>
       </c>
       <c r="F8" t="n">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>1642</v>
+        <v>325</v>
       </c>
       <c r="H8" t="n">
-        <v>24.78</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>534000</v>
+        <v>14390</v>
       </c>
       <c r="K8" t="n">
-        <v>546000</v>
+        <v>15450</v>
       </c>
       <c r="L8" t="n">
-        <v>563000</v>
+        <v>16290</v>
       </c>
       <c r="M8" t="n">
-        <v>512000</v>
+        <v>14040</v>
       </c>
       <c r="N8" t="n">
-        <v>24.86</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>443997596500</v>
+        <v>52559235830</v>
       </c>
       <c r="P8" t="n">
-        <v>723000</v>
+        <v>49800</v>
       </c>
       <c r="Q8" t="n">
-        <v>259000</v>
+        <v>8180</v>
       </c>
       <c r="R8" t="n">
-        <v>-24000</v>
+        <v>-238000</v>
       </c>
       <c r="S8" t="n">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>컨퍼런스콜 기반의 4분기 실적 컨센서스 상회 및 전고체 배터리 상용화 기대. 긍정적인 실적 발표와 미래 전망을 근거로 한 상승 기대.</t>
+          <t>미국 의료 AI 급등과 함께 일부 긍정적 언급이 있으나, 시장 약세 및 차익실현 가능성에 대한 우려 혼재. 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['전고체배터리', '컨퍼런스콜', '실적']</t>
+          <t>['의료AI', '공매도', '차익실현']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14400</v>
+        <v>533000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'-0.19%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>119</v>
+        <v>329</v>
       </c>
       <c r="F9" t="n">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="G9" t="n">
-        <v>323</v>
+        <v>1681</v>
       </c>
       <c r="H9" t="n">
-        <v>8.050000000000001</v>
+        <v>24.78</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14390</v>
+        <v>534000</v>
       </c>
       <c r="K9" t="n">
-        <v>15450</v>
+        <v>546000</v>
       </c>
       <c r="L9" t="n">
-        <v>16290</v>
+        <v>563000</v>
       </c>
       <c r="M9" t="n">
-        <v>14040</v>
+        <v>512000</v>
       </c>
       <c r="N9" t="n">
-        <v>8.109999999999999</v>
+        <v>24.86</v>
       </c>
       <c r="O9" t="n">
-        <v>52324939160</v>
+        <v>450984177500</v>
       </c>
       <c r="P9" t="n">
-        <v>49800</v>
+        <v>723000</v>
       </c>
       <c r="Q9" t="n">
-        <v>8180</v>
+        <v>259000</v>
       </c>
       <c r="R9" t="n">
-        <v>-238000</v>
+        <v>-24000</v>
       </c>
       <c r="S9" t="n">
-        <v>11000</v>
+        <v>9000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 의료 AI 급등과 함께 일부 긍정적 언급이 있으나, 시장 약세 및 차익실현 가능성에 대한 우려 혼재. 공매도 관련 언급.</t>
+          <t>분기 실적 호조 및 컨퍼런스콜 긍정적 내용. 전고체 배터리 상용화 기대감과 함께 연말 최고 실적 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['의료AI', '공매도', '차익실현']</t>
+          <t>['실적 호조', '전고체 배터리', '컨퍼런스콜']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14880</v>
+        <v>14900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.67%</t>
+          <t>'-0.53%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G10" t="n">
-        <v>739</v>
+        <v>777</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>139983357115</v>
+        <v>140510056915</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>광통신 섹터 강세와 루멘텀 인수 가능성 등 긍정적인 뉴스를 바탕으로 연말 목표 주가 3만원을 제시하며 상승 추세를 전망함.</t>
+          <t>미국 시장 호재 및 루멘텀 인수 루머 기반 급등. 광통신 산업 성장 전망과 3만 원 목표 주가 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀 인수', '유리기판']</t>
+          <t>['광통신', '루멘텀 인수', '목표 주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26350</v>
+        <v>26400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.31%</t>
+          <t>'-1.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
         <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H11" t="n">
         <v>12.23</v>
@@ -1438,7 +1438,7 @@
         <v>12.3</v>
       </c>
       <c r="O11" t="n">
-        <v>35544772025</v>
+        <v>36083936825</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62900</v>
+        <v>63100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.02%</t>
+          <t>'-1.71%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G12" t="n">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="H12" t="n">
         <v>41.55</v>
@@ -1530,7 +1530,7 @@
         <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>147432446000</v>
+        <v>149332990500</v>
       </c>
       <c r="P12" t="n">
         <v>67300</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 기대감과 공매도 세력에 대한 경계. 수주 공시 및 신고가 돌파 가능성 언급. 삼성전자 시설 투자 확대 수혜 전망.</t>
+          <t>수주 공시 및 신고가 도전 움직임. 삼성전자 투자 확대 뉴스와 건설 업종 내 상대적 강세 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['자사주 매입', '수주 공시', '삼성전자 투자']</t>
+          <t>['수주 공시', '신고가', '삼성전자 투자']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8830</v>
+        <v>8860</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.81%</t>
+          <t>'-3.49%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H13" t="n">
         <v>0.37</v>
@@ -1622,7 +1622,7 @@
         <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>29819929380</v>
+        <v>29958964580</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15760</v>
+        <v>182600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.54%</t>
+          <t>'-3.95%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="E14" t="n">
         <v>144</v>
       </c>
       <c r="F14" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="G14" t="n">
-        <v>367</v>
+        <v>466</v>
       </c>
       <c r="H14" t="n">
-        <v>28.07</v>
+        <v>75</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16510</v>
+        <v>190100</v>
       </c>
       <c r="K14" t="n">
-        <v>16380</v>
+        <v>189400</v>
       </c>
       <c r="L14" t="n">
-        <v>16440</v>
+        <v>197000</v>
       </c>
       <c r="M14" t="n">
-        <v>15760</v>
+        <v>180800</v>
       </c>
       <c r="N14" t="n">
-        <v>28.03</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>42231718615</v>
+        <v>1186400281250</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>243500</v>
       </c>
       <c r="Q14" t="n">
-        <v>15760</v>
+        <v>71000</v>
       </c>
       <c r="R14" t="n">
-        <v>-48000</v>
+        <v>-409000</v>
       </c>
       <c r="S14" t="n">
-        <v>-70000</v>
+        <v>-172000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 발표 후 주가 하락에 대한 실망감. 중국 조선업체와의 경쟁력 약화 및 향후 전망에 대한 우려. 한국 증권사의 신뢰성 문제 제기.</t>
+          <t>이재용 오너 리스크 및 증여세 문제로 인한 주주환원 불확실성. IR 자료 수준에 대한 비판과 우선주 소각 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적 발표', '조선업', '주가 하락']</t>
+          <t>['오너 리스크', '증여세', '주주환원']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>181000</v>
+        <v>15780</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.79%</t>
+          <t>'-4.42%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F15" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="G15" t="n">
-        <v>444</v>
+        <v>377</v>
       </c>
       <c r="H15" t="n">
-        <v>75</v>
+        <v>28.07</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>190100</v>
+        <v>16510</v>
       </c>
       <c r="K15" t="n">
-        <v>189400</v>
+        <v>16380</v>
       </c>
       <c r="L15" t="n">
-        <v>197000</v>
+        <v>16440</v>
       </c>
       <c r="M15" t="n">
-        <v>180800</v>
+        <v>15760</v>
       </c>
       <c r="N15" t="n">
-        <v>74.90000000000001</v>
+        <v>28.03</v>
       </c>
       <c r="O15" t="n">
-        <v>1175900121400</v>
+        <v>43909474770</v>
       </c>
       <c r="P15" t="n">
-        <v>243500</v>
+        <v>35350</v>
       </c>
       <c r="Q15" t="n">
-        <v>71000</v>
+        <v>15760</v>
       </c>
       <c r="R15" t="n">
-        <v>-409000</v>
+        <v>-48000</v>
       </c>
       <c r="S15" t="n">
-        <v>-172000</v>
+        <v>-70000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>오너 리스크와 주주환원 불확실성에 대한 우려. IR 자료 및 컨퍼런스콜 내용의 허술함 지적. 증여세 문제와 연관된 주가 하락 및 우선주 소각 기대.</t>
+          <t>실적 발표에도 불구하고 주가 하락 지속. 중국 조선업체와의 경쟁 및 한국 증권사 신뢰도 문제 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['오너 리스크', '주주환원', '우선주']</t>
+          <t>['실적 발표', '주가 하락', '조선업 경쟁']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3980</v>
+        <v>3995</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.13%</t>
+          <t>'-4.77%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F16" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G16" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H16" t="n">
         <v>2.2</v>
@@ -1898,7 +1898,7 @@
         <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>162427647320</v>
+        <v>162762140329</v>
       </c>
       <c r="P16" t="n">
         <v>8100</v>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>227500</v>
+        <v>229500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.99%</t>
+          <t>'-5.17%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="G17" t="n">
-        <v>2415</v>
+        <v>2320</v>
       </c>
       <c r="H17" t="n">
         <v>46.19</v>
@@ -1990,7 +1990,7 @@
         <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4020331899500</v>
+        <v>4075005612500</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>컨퍼런스콜 내용에 대한 강한 불만과 경영진 퇴출 요구. 이재용 회장의 경영 능력 및 주주 무시에 대한 비판. 증여세 회피를 위한 주가 조작 의혹 제기.</t>
+          <t>컨퍼런스콜 내용 및 경영진 발표에 대한 불만 고조. 이재용 증여세 문제와 연관된 주가 하락 및 주주환원 불확실성.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['컨퍼런스콜', '이재용', '증여세']</t>
+          <t>['컨퍼런스콜', '증여세', '주주환원']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1849</v>
+        <v>1856</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-11.95%</t>
+          <t>'-11.62%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2082,7 +2082,7 @@
         <v>5.07</v>
       </c>
       <c r="O18" t="n">
-        <v>12508469514</v>
+        <v>12592821824</v>
       </c>
       <c r="P18" t="n">
         <v>4980</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53800</v>
+        <v>54000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-12.38%</t>
+          <t>'-12.05%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G19" t="n">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="H19" t="n">
         <v>22.34</v>
@@ -2174,7 +2174,7 @@
         <v>22.32</v>
       </c>
       <c r="O19" t="n">
-        <v>281306395850</v>
+        <v>285176566950</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16610</v>
+        <v>16670</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-13.53%</t>
+          <t>'-13.22%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F20" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G20" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>89139011875</v>
+        <v>89771661400</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2100</v>
+        <v>2120</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-18.29%</t>
+          <t>'-17.51%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.47</v>
       </c>
       <c r="E21" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F21" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G21" t="n">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="H21" t="n">
         <v>1.22</v>
@@ -2358,7 +2358,7 @@
         <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>15709176545</v>
+        <v>15856932950</v>
       </c>
       <c r="P21" t="n">
         <v>2965</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>실적 부진 및 급격한 주가 하락에 대한 불만. 기타법인 꾸준한 매집에도 불구하고 반등 없는 흐름 지적. 사채 발행 및 롤링 이슈에 대한 우려.</t>
+          <t>급격한 주가 하락 및 사기 의혹 제기. 실적 불확실성과 역망치 패턴 발생에 따른 투자자 불안감 고조.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가 하락', '기타법인', '사채 발행']</t>
+          <t>['주가 하락', '사기 의혹', '역망치']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11540</v>
+        <v>11630</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-19.13%</t>
+          <t>'-18.50%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G22" t="n">
-        <v>2043</v>
+        <v>2135</v>
       </c>
       <c r="H22" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>9.83</v>
       </c>
       <c r="O22" t="n">
-        <v>276525474500</v>
+        <v>281337419020</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>원전 공사 관련 단기 악재 및 과매도 진단. 정치권 개입 및 정부 태도에 대한 비판. 공사비 감액 및 재협상 과정에서 발생한 이슈에 대한 불만.</t>
+          <t>원전 공사 관련 악재 및 정치적 개입 의혹으로 인한 과매도 상태. 재협상 가능성 및 공매도 세력의 움직임 주목.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['원전 공사', '과매도', '정치권 개입']</t>
+          <t>['원전 공사', '정치적 개입', '재협상']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261029_12.xlsx
+++ b/data/trending_integrated_20261029_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
         <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>6804233139</v>
+        <v>6808137179</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9300</v>
+        <v>9320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.40%</t>
+          <t>'+16.65%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>124834462590</v>
+        <v>125465462155</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38300</v>
+        <v>37900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.06%</t>
+          <t>'+8.91%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>107174468325</v>
+        <v>108216652800</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7770</v>
+        <v>7800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.30%</t>
+          <t>'+4.70%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>88</v>
       </c>
       <c r="G5" t="n">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>104637289155</v>
+        <v>105050236575</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>반도체 테마 및 광주 반도체 클러스터 관련 긍정적 전망. 외국인 및 기타법인 매수세 유입 확인. 차트상 상승 추세 및 텐베거 가능성 기대.</t>
+          <t>하이닉스 물량 완판 및 광주반도체 테마 관련 기대감. 외국인 및 기타법인 매수세 확인.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체 테마', '외국인 매수', '차트 분석']</t>
+          <t>['반도체', '테마', '외국인']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1512000</v>
+        <v>1510000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.68%</t>
+          <t>'+1.55%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G6" t="n">
-        <v>1176</v>
+        <v>1199</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.61</v>
       </c>
       <c r="O6" t="n">
-        <v>4841291423000</v>
+        <v>4893093894500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자와의 비교를 통한 SK하이닉스의 상대적 우위 부각. 외인 매수세 유입 및 자사주 매입 효과에 대한 기대감. 향후 시가총액 1위 탈환 가능성 언급.</t>
+          <t>삼성전자와의 차별화된 흐름 및 외인 매수세 유입 확인. 시총 역전 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '삼성전자', '외인 매수']</t>
+          <t>['삼성전자', '외인', '시총']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29150</v>
+        <v>29100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.57%</t>
+          <t>'+1.39%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H7" t="n">
         <v>1.77</v>
@@ -1070,7 +1070,7 @@
         <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>100590088050</v>
+        <v>101440775675</v>
       </c>
       <c r="P7" t="n">
         <v>59600</v>
@@ -1119,18 +1119,18 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14510</v>
+        <v>14390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.83%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F8" t="n">
         <v>75</v>
@@ -1162,7 +1162,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>52559235830</v>
+        <v>52849726520</v>
       </c>
       <c r="P8" t="n">
         <v>49800</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>533000</v>
+        <v>530000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.19%</t>
+          <t>'-0.75%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F9" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G9" t="n">
-        <v>1681</v>
+        <v>1694</v>
       </c>
       <c r="H9" t="n">
         <v>24.78</v>
@@ -1254,7 +1254,7 @@
         <v>24.86</v>
       </c>
       <c r="O9" t="n">
-        <v>450984177500</v>
+        <v>460412326500</v>
       </c>
       <c r="P9" t="n">
         <v>723000</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14900</v>
+        <v>14830</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.53%</t>
+          <t>'-1.00%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F10" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" t="n">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>140510056915</v>
+        <v>141166530380</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26400</v>
+        <v>26250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.12%</t>
+          <t>'-1.69%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F11" t="n">
         <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="H11" t="n">
         <v>12.23</v>
@@ -1438,7 +1438,7 @@
         <v>12.3</v>
       </c>
       <c r="O11" t="n">
-        <v>36083936825</v>
+        <v>36682738425</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63100</v>
+        <v>63000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.71%</t>
+          <t>'-1.87%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12" t="n">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="H12" t="n">
         <v>41.55</v>
@@ -1530,7 +1530,7 @@
         <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>149332990500</v>
+        <v>150874454150</v>
       </c>
       <c r="P12" t="n">
         <v>67300</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8860</v>
+        <v>8850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.49%</t>
+          <t>'-3.59%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H13" t="n">
         <v>0.37</v>
@@ -1622,7 +1622,7 @@
         <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>29958964580</v>
+        <v>30037357815</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>182600</v>
+        <v>182200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.95%</t>
+          <t>'-4.16%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G14" t="n">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="H14" t="n">
         <v>75</v>
@@ -1714,7 +1714,7 @@
         <v>74.90000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>1186400281250</v>
+        <v>1197820671600</v>
       </c>
       <c r="P14" t="n">
         <v>243500</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>이재용 오너 리스크 및 증여세 문제로 인한 주주환원 불확실성. IR 자료 수준에 대한 비판과 우선주 소각 기대.</t>
+          <t>오너 리스크와 주주환원 불확실성에 대한 부정적 전망. IR 내용 비판.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['오너 리스크', '증여세', '주주환원']</t>
+          <t>['오너 리스크', '주주환원', 'IR']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,70 +1759,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15780</v>
+        <v>4010</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.42%</t>
+          <t>'-4.41%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="F15" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
-        <v>377</v>
+        <v>323</v>
       </c>
       <c r="H15" t="n">
-        <v>28.07</v>
+        <v>2.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>16510</v>
+        <v>4195</v>
       </c>
       <c r="K15" t="n">
-        <v>16380</v>
+        <v>4280</v>
       </c>
       <c r="L15" t="n">
-        <v>16440</v>
+        <v>4480</v>
       </c>
       <c r="M15" t="n">
-        <v>15760</v>
+        <v>3915</v>
       </c>
       <c r="N15" t="n">
-        <v>28.03</v>
+        <v>1.2</v>
       </c>
       <c r="O15" t="n">
-        <v>43909474770</v>
+        <v>163033687054</v>
       </c>
       <c r="P15" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q15" t="n">
-        <v>15760</v>
+        <v>592</v>
       </c>
       <c r="R15" t="n">
-        <v>-48000</v>
+        <v>-190000</v>
       </c>
       <c r="S15" t="n">
-        <v>-70000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>실적 발표에도 불구하고 주가 하락 지속. 중국 조선업체와의 경쟁 및 한국 증권사 신뢰도 문제 제기.</t>
+          <t>글로벌 기업 공급 시작 및 5G 상용화 관련 긍정적 뉴스에도 불구하고 주가 하락. 미국 시장 진출의 어려움 및 광통신 섹터 내 경쟁 심화 우려. 단타 세력의 차익 실현.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['실적 발표', '주가 하락', '조선업 경쟁']</t>
+          <t>['5G 상용화', '광통신', '미국 시장']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3995</v>
+        <v>15780</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.77%</t>
+          <t>'-4.42%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="F16" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>316</v>
+        <v>395</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2</v>
+        <v>28.07</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4195</v>
+        <v>16510</v>
       </c>
       <c r="K16" t="n">
-        <v>4280</v>
+        <v>16380</v>
       </c>
       <c r="L16" t="n">
-        <v>4480</v>
+        <v>16440</v>
       </c>
       <c r="M16" t="n">
-        <v>3915</v>
+        <v>15750</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2</v>
+        <v>28.03</v>
       </c>
       <c r="O16" t="n">
-        <v>162762140329</v>
+        <v>44967893885</v>
       </c>
       <c r="P16" t="n">
-        <v>8100</v>
+        <v>35350</v>
       </c>
       <c r="Q16" t="n">
-        <v>592</v>
+        <v>15750</v>
       </c>
       <c r="R16" t="n">
-        <v>-190000</v>
+        <v>-48000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-70000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>글로벌 기업 공급 시작 및 5G 상용화 관련 긍정적 뉴스에도 불구하고 주가 하락. 미국 시장 진출의 어려움 및 광통신 섹터 내 경쟁 심화 우려. 단타 세력의 차익 실현.</t>
+          <t>실적 발표 후 주가 하락 지속 및 중국 조선업체와의 경쟁력 약화 우려. 사기 국장 비판.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['5G 상용화', '광통신', '미국 시장']</t>
+          <t>['실적', '조선업', '주가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="G17" t="n">
-        <v>2320</v>
+        <v>2351</v>
       </c>
       <c r="H17" t="n">
         <v>46.19</v>
@@ -1990,7 +1990,7 @@
         <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4075005612500</v>
+        <v>4133404213250</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>컨퍼런스콜 내용 및 경영진 발표에 대한 불만 고조. 이재용 증여세 문제와 연관된 주가 하락 및 주주환원 불확실성.</t>
+          <t>컨퍼런스콜 내용 및 주주환원 정책에 대한 강한 불만 제기. 경영진 및 이재용 관련 비판.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['컨퍼런스콜', '증여세', '주주환원']</t>
+          <t>['컨퍼런스콜', '주주환원', '이재용']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1856</v>
+        <v>1863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-11.62%</t>
+          <t>'-11.29%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.28</v>
       </c>
       <c r="E18" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
         <v>152</v>
@@ -2082,7 +2082,7 @@
         <v>5.07</v>
       </c>
       <c r="O18" t="n">
-        <v>12592821824</v>
+        <v>12654421395</v>
       </c>
       <c r="P18" t="n">
         <v>4980</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>54000</v>
+        <v>53800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-12.05%</t>
+          <t>'-12.38%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G19" t="n">
-        <v>2142</v>
+        <v>2154</v>
       </c>
       <c r="H19" t="n">
         <v>22.34</v>
@@ -2174,7 +2174,7 @@
         <v>22.32</v>
       </c>
       <c r="O19" t="n">
-        <v>285176566950</v>
+        <v>291157859250</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16670</v>
+        <v>16640</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-13.22%</t>
+          <t>'-13.38%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F20" t="n">
         <v>59</v>
       </c>
       <c r="G20" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>89771661400</v>
+        <v>90225990130</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 물량 폭탄 우려 속 하락 전망. 반도체 호황에도 불구하고 개별적인 악재에 대한 부정적 언급.</t>
+          <t>보호예수 물량 출회에 따른 급락 가능성 경고. 반도체 업황 둔화 우려.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체', '하락']</t>
+          <t>['보호예수', '반도체', '급락']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2120</v>
+        <v>2110</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-17.51%</t>
+          <t>'-17.90%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.47</v>
       </c>
       <c r="E21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G21" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H21" t="n">
         <v>1.22</v>
@@ -2358,7 +2358,7 @@
         <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>15856932950</v>
+        <v>15998076700</v>
       </c>
       <c r="P21" t="n">
         <v>2965</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11630</v>
+        <v>11610</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-18.50%</t>
+          <t>'-18.64%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G22" t="n">
-        <v>2135</v>
+        <v>2194</v>
       </c>
       <c r="H22" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>9.83</v>
       </c>
       <c r="O22" t="n">
-        <v>281337419020</v>
+        <v>285124981160</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>원전 공사 관련 악재 및 정치적 개입 의혹으로 인한 과매도 상태. 재협상 가능성 및 공매도 세력의 움직임 주목.</t>
+          <t>원전 공사 협상 결렬 관련 논란 및 정치권 개입 의혹 제기. 외국인 순매수 확인.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['원전 공사', '정치적 개입', '재협상']</t>
+          <t>['원전', '협상', '외국인']</t>
         </is>
       </c>
       <c r="X22" t="n">
